--- a/output/2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -536,7 +536,6 @@
           <t>05 72 63 290</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Confermato (TIS, sito Bartog, odpiralnicasi.com). Attivita' primaria ricambi auto, con reparto utensili dedicato. Email del punto vendita non reperibile in forma affidabile, lasciata vuota.</t>
@@ -574,10 +573,9 @@
           <t>01 759 07 53</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Indirizzo confermato (TIS, odpiralnicasi.com). Telefono trovato tramite ricerca (assente nella lista grezza originale). Stesso gruppo Bartog d.o.o. Trebnje.</t>
+          <t>Indirizzo confermato (TIS, odpiralnicasi.com). Telefono trovato tramite ricerca (assente nella lista grezza originale). Stesso gruppo Bartog d.o.o. Trebnje. [DUPLICATO — vedi anche: 2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,10 +610,9 @@
           <t>05 714 19 20</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Indirizzo esatto (Bazoviška 38) e telefono trovati tramite ricerca (odpiralnicasi.com). Fonti indicano attivita' primaria ricambi auto; reparto utensili presente a livello di rete nazionale Bartog.</t>
+          <t>Indirizzo esatto (Bazoviška 38) e telefono trovati tramite ricerca (odpiralnicasi.com). Fonti indicano attivita' primaria ricambi auto; reparto utensili presente a livello di rete nazionale Bartog. [DUPLICATO — vedi anche: 2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
